--- a/public/data/transtubari-datos-2026.xlsx
+++ b/public/data/transtubari-datos-2026.xlsx
@@ -940,10 +940,10 @@
         <v>2026</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         <v>2026</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -988,10 +988,10 @@
         <v>2026</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3253,10 +3253,10 @@
         <v>2026</v>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3277,10 +3277,10 @@
         <v>2026</v>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3301,10 +3301,10 @@
         <v>2026</v>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>2</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>2</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>2</v>
       </c>
       <c r="D100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>2</v>
       </c>
       <c r="D101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>2</v>
       </c>
       <c r="D102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>2</v>
       </c>
       <c r="D103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>2</v>
       </c>
       <c r="D105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>2</v>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>2</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>2</v>
       </c>
       <c r="D109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>2</v>
       </c>
       <c r="D110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>2</v>
       </c>
       <c r="D111" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>2</v>
       </c>
       <c r="D112" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>2</v>
       </c>
       <c r="D113" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>2</v>
       </c>
       <c r="D114" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>2</v>
       </c>
       <c r="D115" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>2</v>
       </c>
       <c r="D116" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>2</v>
       </c>
       <c r="D117" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>2</v>
       </c>
       <c r="D118" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>2</v>
       </c>
       <c r="D119" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>2</v>
       </c>
       <c r="D120" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>2</v>
       </c>
       <c r="D121" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>2</v>
       </c>
       <c r="D122" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>2</v>
       </c>
       <c r="D123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>2</v>
       </c>
       <c r="D124" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>2</v>
       </c>
       <c r="D125" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>2</v>
       </c>
       <c r="D126" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>2</v>
       </c>
       <c r="D127" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>2</v>
       </c>
       <c r="D128" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>2</v>
       </c>
       <c r="D129" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>2</v>
       </c>
       <c r="D130" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>2</v>
       </c>
       <c r="D131" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>2</v>
       </c>
       <c r="D132" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>2</v>
       </c>
       <c r="D133" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>2</v>
       </c>
       <c r="D134" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>2</v>
       </c>
       <c r="D135" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>2</v>
       </c>
       <c r="D136" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>2</v>
       </c>
       <c r="D137" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>2</v>
       </c>
       <c r="D138" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>2</v>
       </c>
       <c r="D139" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>2</v>
       </c>
       <c r="D140" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>2</v>
       </c>
       <c r="D141" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>2</v>
       </c>
       <c r="D142" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>2</v>
       </c>
       <c r="D143" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>2</v>
       </c>
       <c r="D144" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>2</v>
       </c>
       <c r="D145" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>2</v>
       </c>
       <c r="D146" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>2</v>
       </c>
       <c r="D147" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>2</v>
       </c>
       <c r="D148" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>2</v>
       </c>
       <c r="D149" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>2</v>
       </c>
       <c r="D150" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>2</v>
       </c>
       <c r="D151" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>2</v>
       </c>
       <c r="D152" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>2</v>
       </c>
       <c r="D153" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>2</v>
       </c>
       <c r="D154" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>2</v>
       </c>
       <c r="D155" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>2</v>
       </c>
       <c r="D156" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>2</v>
       </c>
       <c r="D157" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2</v>
       </c>
       <c r="D158" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>2</v>
       </c>
       <c r="D159" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>2</v>
       </c>
       <c r="D160" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>2</v>
       </c>
       <c r="D161" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>2</v>
       </c>
       <c r="D162" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>2</v>
       </c>
       <c r="D163" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>2</v>
       </c>
       <c r="D164" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>2</v>
       </c>
       <c r="D165" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>2</v>
       </c>
       <c r="D166" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>2</v>
       </c>
       <c r="D167" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>2</v>
       </c>
       <c r="D168" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>2</v>
       </c>
       <c r="D169" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>2</v>
       </c>
       <c r="D170" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>2</v>
       </c>
       <c r="D171" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>2</v>
       </c>
       <c r="D172" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>2</v>
       </c>
       <c r="D173" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>2</v>
       </c>
       <c r="D174" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>2</v>
       </c>
       <c r="D175" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>2</v>
       </c>
       <c r="D176" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>2</v>
       </c>
       <c r="D177" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5369,10 +5369,10 @@
         <v>2026</v>
       </c>
       <c r="C178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5393,10 +5393,10 @@
         <v>2026</v>
       </c>
       <c r="C179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -5417,10 +5417,10 @@
         <v>2026</v>
       </c>
       <c r="C180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>3</v>
       </c>
       <c r="D181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>3</v>
       </c>
       <c r="D182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>3</v>
       </c>
       <c r="D183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>3</v>
       </c>
       <c r="D184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>3</v>
       </c>
       <c r="D185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>3</v>
       </c>
       <c r="D186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>3</v>
       </c>
       <c r="D187" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>3</v>
       </c>
       <c r="D188" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>3</v>
       </c>
       <c r="D189" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>3</v>
       </c>
       <c r="D190" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>3</v>
       </c>
       <c r="D191" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>3</v>
       </c>
       <c r="D192" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>3</v>
       </c>
       <c r="D193" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>3</v>
       </c>
       <c r="D194" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>3</v>
       </c>
       <c r="D195" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>3</v>
       </c>
       <c r="D196" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>3</v>
       </c>
       <c r="D197" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>3</v>
       </c>
       <c r="D198" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>3</v>
       </c>
       <c r="D199" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>3</v>
       </c>
       <c r="D200" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>3</v>
       </c>
       <c r="D201" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>3</v>
       </c>
       <c r="D202" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>3</v>
       </c>
       <c r="D203" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>3</v>
       </c>
       <c r="D204" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>3</v>
       </c>
       <c r="D205" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>3</v>
       </c>
       <c r="D206" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>3</v>
       </c>
       <c r="D207" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>3</v>
       </c>
       <c r="D208" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>3</v>
       </c>
       <c r="D209" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>3</v>
       </c>
       <c r="D210" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>3</v>
       </c>
       <c r="D211" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>3</v>
       </c>
       <c r="D212" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>3</v>
       </c>
       <c r="D213" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>3</v>
       </c>
       <c r="D214" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>3</v>
       </c>
       <c r="D215" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>3</v>
       </c>
       <c r="D216" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>3</v>
       </c>
       <c r="D217" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>3</v>
       </c>
       <c r="D218" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>3</v>
       </c>
       <c r="D219" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>3</v>
       </c>
       <c r="D220" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>3</v>
       </c>
       <c r="D221" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>3</v>
       </c>
       <c r="D222" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>3</v>
       </c>
       <c r="D223" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>3</v>
       </c>
       <c r="D224" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>3</v>
       </c>
       <c r="D225" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>3</v>
       </c>
       <c r="D226" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>3</v>
       </c>
       <c r="D227" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>3</v>
       </c>
       <c r="D228" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>3</v>
       </c>
       <c r="D229" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>3</v>
       </c>
       <c r="D230" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>3</v>
       </c>
       <c r="D231" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>3</v>
       </c>
       <c r="D232" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>3</v>
       </c>
       <c r="D233" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>3</v>
       </c>
       <c r="D234" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>3</v>
       </c>
       <c r="D235" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>3</v>
       </c>
       <c r="D236" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>3</v>
       </c>
       <c r="D237" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>3</v>
       </c>
       <c r="D238" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>3</v>
       </c>
       <c r="D239" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>3</v>
       </c>
       <c r="D240" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>3</v>
       </c>
       <c r="D241" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>3</v>
       </c>
       <c r="D242" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>3</v>
       </c>
       <c r="D243" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>3</v>
       </c>
       <c r="D244" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>3</v>
       </c>
       <c r="D245" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>3</v>
       </c>
       <c r="D246" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>3</v>
       </c>
       <c r="D247" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>3</v>
       </c>
       <c r="D248" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>3</v>
       </c>
       <c r="D249" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>3</v>
       </c>
       <c r="D250" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>3</v>
       </c>
       <c r="D251" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>3</v>
       </c>
       <c r="D252" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>3</v>
       </c>
       <c r="D253" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>3</v>
       </c>
       <c r="D254" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>3</v>
       </c>
       <c r="D255" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>3</v>
       </c>
       <c r="D256" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>3</v>
       </c>
       <c r="D257" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>3</v>
       </c>
       <c r="D258" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>3</v>
       </c>
       <c r="D259" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>3</v>
       </c>
       <c r="D260" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>3</v>
       </c>
       <c r="D261" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>3</v>
       </c>
       <c r="D262" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>3</v>
       </c>
       <c r="D263" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>3</v>
       </c>
       <c r="D264" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>3</v>
       </c>
       <c r="D265" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>3</v>
       </c>
       <c r="D266" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>3</v>
       </c>
       <c r="D267" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>3</v>
       </c>
       <c r="D268" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -7663,10 +7663,10 @@
         <v>2026</v>
       </c>
       <c r="C269" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D269" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -7692,10 +7692,10 @@
         <v>2026</v>
       </c>
       <c r="C270" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D270" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -7716,10 +7716,10 @@
         <v>2026</v>
       </c>
       <c r="C271" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D271" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>4</v>
       </c>
       <c r="D272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>4</v>
       </c>
       <c r="D273" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>4</v>
       </c>
       <c r="D274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>4</v>
       </c>
       <c r="D275" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>4</v>
       </c>
       <c r="D276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>4</v>
       </c>
       <c r="D277" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>4</v>
       </c>
       <c r="D278" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>4</v>
       </c>
       <c r="D279" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>4</v>
       </c>
       <c r="D280" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>4</v>
       </c>
       <c r="D281" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>4</v>
       </c>
       <c r="D282" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>4</v>
       </c>
       <c r="D283" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>4</v>
       </c>
       <c r="D284" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>4</v>
       </c>
       <c r="D285" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>4</v>
       </c>
       <c r="D286" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>4</v>
       </c>
       <c r="D287" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>4</v>
       </c>
       <c r="D288" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>4</v>
       </c>
       <c r="D289" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>4</v>
       </c>
       <c r="D290" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>4</v>
       </c>
       <c r="D291" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>4</v>
       </c>
       <c r="D292" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>4</v>
       </c>
       <c r="D293" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>4</v>
       </c>
       <c r="D294" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>4</v>
       </c>
       <c r="D295" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>4</v>
       </c>
       <c r="D296" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>4</v>
       </c>
       <c r="D297" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>4</v>
       </c>
       <c r="D298" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>4</v>
       </c>
       <c r="D299" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>4</v>
       </c>
       <c r="D300" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>4</v>
       </c>
       <c r="D301" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>4</v>
       </c>
       <c r="D302" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>4</v>
       </c>
       <c r="D303" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>4</v>
       </c>
       <c r="D304" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>4</v>
       </c>
       <c r="D305" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>4</v>
       </c>
       <c r="D306" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>4</v>
       </c>
       <c r="D307" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>4</v>
       </c>
       <c r="D308" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>4</v>
       </c>
       <c r="D309" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>4</v>
       </c>
       <c r="D310" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>4</v>
       </c>
       <c r="D311" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>4</v>
       </c>
       <c r="D312" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>4</v>
       </c>
       <c r="D313" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>4</v>
       </c>
       <c r="D314" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>4</v>
       </c>
       <c r="D315" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>4</v>
       </c>
       <c r="D316" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>4</v>
       </c>
       <c r="D317" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>4</v>
       </c>
       <c r="D318" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>4</v>
       </c>
       <c r="D319" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>4</v>
       </c>
       <c r="D320" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>4</v>
       </c>
       <c r="D321" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>4</v>
       </c>
       <c r="D322" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>4</v>
       </c>
       <c r="D323" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>4</v>
       </c>
       <c r="D324" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>4</v>
       </c>
       <c r="D325" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>4</v>
       </c>
       <c r="D326" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>4</v>
       </c>
       <c r="D327" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>4</v>
       </c>
       <c r="D328" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>4</v>
       </c>
       <c r="D329" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>4</v>
       </c>
       <c r="D330" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>4</v>
       </c>
       <c r="D331" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>4</v>
       </c>
       <c r="D332" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>4</v>
       </c>
       <c r="D333" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>4</v>
       </c>
       <c r="D334" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>4</v>
       </c>
       <c r="D335" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>4</v>
       </c>
       <c r="D336" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>4</v>
       </c>
       <c r="D337" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>4</v>
       </c>
       <c r="D338" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>4</v>
       </c>
       <c r="D339" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>4</v>
       </c>
       <c r="D340" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>4</v>
       </c>
       <c r="D341" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>4</v>
       </c>
       <c r="D342" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>4</v>
       </c>
       <c r="D343" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>4</v>
       </c>
       <c r="D344" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>4</v>
       </c>
       <c r="D345" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>4</v>
       </c>
       <c r="D346" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>4</v>
       </c>
       <c r="D347" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>4</v>
       </c>
       <c r="D348" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>4</v>
       </c>
       <c r="D349" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>4</v>
       </c>
       <c r="D350" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>4</v>
       </c>
       <c r="D351" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>4</v>
       </c>
       <c r="D352" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>4</v>
       </c>
       <c r="D353" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>4</v>
       </c>
       <c r="D354" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>4</v>
       </c>
       <c r="D355" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>4</v>
       </c>
       <c r="D356" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -9795,10 +9795,10 @@
         <v>2026</v>
       </c>
       <c r="C357" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D357" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -9819,10 +9819,10 @@
         <v>2026</v>
       </c>
       <c r="C358" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D358" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -9843,10 +9843,10 @@
         <v>2026</v>
       </c>
       <c r="C359" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D359" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>5</v>
       </c>
       <c r="D360" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>5</v>
       </c>
       <c r="D361" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>5</v>
       </c>
       <c r="D362" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>5</v>
       </c>
       <c r="D363" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>5</v>
       </c>
       <c r="D364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>5</v>
       </c>
       <c r="D365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>5</v>
       </c>
       <c r="D366" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>5</v>
       </c>
       <c r="D367" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>5</v>
       </c>
       <c r="D368" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>5</v>
       </c>
       <c r="D369" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>5</v>
       </c>
       <c r="D370" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>5</v>
       </c>
       <c r="D371" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>5</v>
       </c>
       <c r="D372" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>5</v>
       </c>
       <c r="D373" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>5</v>
       </c>
       <c r="D374" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>5</v>
       </c>
       <c r="D375" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>5</v>
       </c>
       <c r="D376" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>5</v>
       </c>
       <c r="D377" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>5</v>
       </c>
       <c r="D378" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>5</v>
       </c>
       <c r="D379" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>5</v>
       </c>
       <c r="D380" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>5</v>
       </c>
       <c r="D381" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>5</v>
       </c>
       <c r="D382" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>5</v>
       </c>
       <c r="D383" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>5</v>
       </c>
       <c r="D384" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>5</v>
       </c>
       <c r="D385" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>5</v>
       </c>
       <c r="D386" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>5</v>
       </c>
       <c r="D387" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>5</v>
       </c>
       <c r="D388" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>5</v>
       </c>
       <c r="D389" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>5</v>
       </c>
       <c r="D390" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>5</v>
       </c>
       <c r="D391" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>5</v>
       </c>
       <c r="D392" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>5</v>
       </c>
       <c r="D393" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>5</v>
       </c>
       <c r="D394" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>5</v>
       </c>
       <c r="D395" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>5</v>
       </c>
       <c r="D396" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>5</v>
       </c>
       <c r="D397" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>5</v>
       </c>
       <c r="D398" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>5</v>
       </c>
       <c r="D399" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>5</v>
       </c>
       <c r="D400" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>5</v>
       </c>
       <c r="D401" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>5</v>
       </c>
       <c r="D402" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>5</v>
       </c>
       <c r="D403" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>5</v>
       </c>
       <c r="D404" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>5</v>
       </c>
       <c r="D405" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>5</v>
       </c>
       <c r="D406" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>5</v>
       </c>
       <c r="D407" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>5</v>
       </c>
       <c r="D408" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>5</v>
       </c>
       <c r="D409" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>5</v>
       </c>
       <c r="D410" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>5</v>
       </c>
       <c r="D411" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>5</v>
       </c>
       <c r="D412" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>5</v>
       </c>
       <c r="D413" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>5</v>
       </c>
       <c r="D414" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>5</v>
       </c>
       <c r="D415" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>5</v>
       </c>
       <c r="D416" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>5</v>
       </c>
       <c r="D417" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>5</v>
       </c>
       <c r="D418" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>5</v>
       </c>
       <c r="D419" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>5</v>
       </c>
       <c r="D420" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>5</v>
       </c>
       <c r="D421" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>5</v>
       </c>
       <c r="D422" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>5</v>
       </c>
       <c r="D423" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>5</v>
       </c>
       <c r="D424" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>5</v>
       </c>
       <c r="D425" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>5</v>
       </c>
       <c r="D426" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>5</v>
       </c>
       <c r="D427" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>5</v>
       </c>
       <c r="D428" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>5</v>
       </c>
       <c r="D429" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>5</v>
       </c>
       <c r="D430" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>5</v>
       </c>
       <c r="D431" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>5</v>
       </c>
       <c r="D432" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>5</v>
       </c>
       <c r="D433" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>5</v>
       </c>
       <c r="D434" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E434" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>5</v>
       </c>
       <c r="D435" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E435" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>5</v>
       </c>
       <c r="D436" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>5</v>
       </c>
       <c r="D437" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>5</v>
       </c>
       <c r="D438" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>5</v>
       </c>
       <c r="D439" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>5</v>
       </c>
       <c r="D440" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>5</v>
       </c>
       <c r="D441" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>5</v>
       </c>
       <c r="D442" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>5</v>
       </c>
       <c r="D443" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>5</v>
       </c>
       <c r="D444" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>5</v>
       </c>
       <c r="D445" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>5</v>
       </c>
       <c r="D446" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>5</v>
       </c>
       <c r="D447" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
@@ -11979,10 +11979,10 @@
         <v>2026</v>
       </c>
       <c r="C448" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D448" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
@@ -12003,10 +12003,10 @@
         <v>2026</v>
       </c>
       <c r="C449" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D449" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
@@ -12027,10 +12027,10 @@
         <v>2026</v>
       </c>
       <c r="C450" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D450" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>6</v>
       </c>
       <c r="D451" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E451" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>6</v>
       </c>
       <c r="D452" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E452" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>6</v>
       </c>
       <c r="D453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E453" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>6</v>
       </c>
       <c r="D454" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>6</v>
       </c>
       <c r="D455" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E455" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>6</v>
       </c>
       <c r="D456" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E456" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>6</v>
       </c>
       <c r="D457" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>6</v>
       </c>
       <c r="D458" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>6</v>
       </c>
       <c r="D459" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>6</v>
       </c>
       <c r="D460" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>6</v>
       </c>
       <c r="D461" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>6</v>
       </c>
       <c r="D462" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>6</v>
       </c>
       <c r="D463" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E463" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>6</v>
       </c>
       <c r="D464" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>6</v>
       </c>
       <c r="D465" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>6</v>
       </c>
       <c r="D466" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>6</v>
       </c>
       <c r="D467" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>6</v>
       </c>
       <c r="D468" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E468" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="D469" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>6</v>
       </c>
       <c r="D470" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>6</v>
       </c>
       <c r="D471" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>6</v>
       </c>
       <c r="D472" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>6</v>
       </c>
       <c r="D473" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>6</v>
       </c>
       <c r="D474" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>6</v>
       </c>
       <c r="D475" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>6</v>
       </c>
       <c r="D476" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>6</v>
       </c>
       <c r="D477" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>6</v>
       </c>
       <c r="D478" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>6</v>
       </c>
       <c r="D479" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>6</v>
       </c>
       <c r="D480" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E480" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>6</v>
       </c>
       <c r="D481" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E481" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>6</v>
       </c>
       <c r="D482" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E482" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>6</v>
       </c>
       <c r="D483" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E483" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>6</v>
       </c>
       <c r="D484" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E484" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>6</v>
       </c>
       <c r="D485" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E485" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>6</v>
       </c>
       <c r="D486" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E486" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>6</v>
       </c>
       <c r="D487" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>6</v>
       </c>
       <c r="D488" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E488" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>6</v>
       </c>
       <c r="D489" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E489" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>6</v>
       </c>
       <c r="D490" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>6</v>
       </c>
       <c r="D491" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>6</v>
       </c>
       <c r="D492" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E492" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>6</v>
       </c>
       <c r="D493" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E493" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>6</v>
       </c>
       <c r="D494" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E494" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>6</v>
       </c>
       <c r="D495" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E495" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>6</v>
       </c>
       <c r="D496" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E496" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>6</v>
       </c>
       <c r="D497" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E497" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>6</v>
       </c>
       <c r="D498" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E498" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>6</v>
       </c>
       <c r="D499" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E499" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>6</v>
       </c>
       <c r="D500" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E500" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>6</v>
       </c>
       <c r="D501" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E501" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>6</v>
       </c>
       <c r="D502" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E502" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="D503" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>6</v>
       </c>
       <c r="D504" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>6</v>
       </c>
       <c r="D505" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E505" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>6</v>
       </c>
       <c r="D506" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E506" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>6</v>
       </c>
       <c r="D507" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E507" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>6</v>
       </c>
       <c r="D508" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>6</v>
       </c>
       <c r="D509" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E509" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>6</v>
       </c>
       <c r="D510" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E510" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>6</v>
       </c>
       <c r="D511" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E511" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>6</v>
       </c>
       <c r="D512" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E512" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>6</v>
       </c>
       <c r="D513" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E513" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>6</v>
       </c>
       <c r="D514" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E514" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>6</v>
       </c>
       <c r="D515" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E515" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>6</v>
       </c>
       <c r="D516" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E516" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>6</v>
       </c>
       <c r="D517" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E517" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>6</v>
       </c>
       <c r="D518" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E518" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>6</v>
       </c>
       <c r="D519" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E519" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>6</v>
       </c>
       <c r="D520" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E520" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>6</v>
       </c>
       <c r="D521" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E521" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>6</v>
       </c>
       <c r="D522" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E522" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>6</v>
       </c>
       <c r="D523" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E523" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>6</v>
       </c>
       <c r="D524" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E524" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>6</v>
       </c>
       <c r="D525" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E525" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>6</v>
       </c>
       <c r="D526" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E526" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>6</v>
       </c>
       <c r="D527" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E527" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>6</v>
       </c>
       <c r="D528" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E528" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>6</v>
       </c>
       <c r="D529" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E529" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>6</v>
       </c>
       <c r="D530" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E530" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>6</v>
       </c>
       <c r="D531" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E531" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>6</v>
       </c>
       <c r="D532" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E532" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>6</v>
       </c>
       <c r="D533" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E533" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>6</v>
       </c>
       <c r="D534" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E534" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>6</v>
       </c>
       <c r="D535" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E535" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>6</v>
       </c>
       <c r="D536" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E536" t="inlineStr">
         <is>
@@ -14115,10 +14115,10 @@
         <v>2026</v>
       </c>
       <c r="C537" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D537" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
@@ -14139,10 +14139,10 @@
         <v>2026</v>
       </c>
       <c r="C538" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D538" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E538" t="inlineStr">
         <is>
@@ -14163,10 +14163,10 @@
         <v>2026</v>
       </c>
       <c r="C539" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D539" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E539" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>7</v>
       </c>
       <c r="D540" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E540" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>7</v>
       </c>
       <c r="D541" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E541" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>7</v>
       </c>
       <c r="D542" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E542" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>7</v>
       </c>
       <c r="D543" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E543" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>7</v>
       </c>
       <c r="D544" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E544" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>7</v>
       </c>
       <c r="D545" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E545" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>7</v>
       </c>
       <c r="D546" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E546" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>7</v>
       </c>
       <c r="D547" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E547" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>7</v>
       </c>
       <c r="D548" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E548" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>7</v>
       </c>
       <c r="D549" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E549" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>7</v>
       </c>
       <c r="D550" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E550" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>7</v>
       </c>
       <c r="D551" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E551" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>7</v>
       </c>
       <c r="D552" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E552" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>7</v>
       </c>
       <c r="D553" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E553" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>7</v>
       </c>
       <c r="D554" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E554" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>7</v>
       </c>
       <c r="D555" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E555" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>7</v>
       </c>
       <c r="D556" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E556" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>7</v>
       </c>
       <c r="D557" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E557" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>7</v>
       </c>
       <c r="D558" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E558" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>7</v>
       </c>
       <c r="D559" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E559" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>7</v>
       </c>
       <c r="D560" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E560" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>7</v>
       </c>
       <c r="D561" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E561" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>7</v>
       </c>
       <c r="D562" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E562" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>7</v>
       </c>
       <c r="D563" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E563" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>7</v>
       </c>
       <c r="D564" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E564" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>7</v>
       </c>
       <c r="D565" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E565" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>7</v>
       </c>
       <c r="D566" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E566" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>7</v>
       </c>
       <c r="D567" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E567" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>7</v>
       </c>
       <c r="D568" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E568" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>7</v>
       </c>
       <c r="D569" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E569" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>7</v>
       </c>
       <c r="D570" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E570" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>7</v>
       </c>
       <c r="D571" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E571" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>7</v>
       </c>
       <c r="D572" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E572" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>7</v>
       </c>
       <c r="D573" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E573" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>7</v>
       </c>
       <c r="D574" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E574" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>7</v>
       </c>
       <c r="D575" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E575" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>7</v>
       </c>
       <c r="D576" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E576" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>7</v>
       </c>
       <c r="D577" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E577" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>7</v>
       </c>
       <c r="D578" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E578" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>7</v>
       </c>
       <c r="D579" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E579" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>7</v>
       </c>
       <c r="D580" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E580" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>7</v>
       </c>
       <c r="D581" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E581" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
         <v>7</v>
       </c>
       <c r="D582" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E582" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>7</v>
       </c>
       <c r="D583" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E583" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>7</v>
       </c>
       <c r="D584" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E584" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>7</v>
       </c>
       <c r="D585" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E585" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>7</v>
       </c>
       <c r="D586" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E586" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>7</v>
       </c>
       <c r="D587" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E587" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>7</v>
       </c>
       <c r="D588" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E588" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>7</v>
       </c>
       <c r="D589" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E589" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>7</v>
       </c>
       <c r="D590" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E590" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>7</v>
       </c>
       <c r="D591" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E591" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>7</v>
       </c>
       <c r="D592" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E592" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>7</v>
       </c>
       <c r="D593" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E593" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>7</v>
       </c>
       <c r="D594" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E594" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>7</v>
       </c>
       <c r="D595" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E595" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>7</v>
       </c>
       <c r="D596" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E596" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>7</v>
       </c>
       <c r="D597" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E597" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>7</v>
       </c>
       <c r="D598" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E598" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>7</v>
       </c>
       <c r="D599" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E599" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>7</v>
       </c>
       <c r="D600" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E600" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>7</v>
       </c>
       <c r="D601" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E601" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>7</v>
       </c>
       <c r="D602" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E602" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>7</v>
       </c>
       <c r="D603" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E603" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>7</v>
       </c>
       <c r="D604" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E604" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>7</v>
       </c>
       <c r="D605" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E605" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>7</v>
       </c>
       <c r="D606" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E606" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>7</v>
       </c>
       <c r="D607" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E607" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>7</v>
       </c>
       <c r="D608" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E608" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>7</v>
       </c>
       <c r="D609" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E609" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>7</v>
       </c>
       <c r="D610" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E610" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>7</v>
       </c>
       <c r="D611" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E611" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>7</v>
       </c>
       <c r="D612" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E612" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>7</v>
       </c>
       <c r="D613" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E613" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>7</v>
       </c>
       <c r="D614" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E614" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>7</v>
       </c>
       <c r="D615" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E615" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>7</v>
       </c>
       <c r="D616" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E616" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>7</v>
       </c>
       <c r="D617" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E617" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>7</v>
       </c>
       <c r="D618" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E618" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>7</v>
       </c>
       <c r="D619" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E619" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>7</v>
       </c>
       <c r="D620" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E620" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>7</v>
       </c>
       <c r="D621" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E621" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>7</v>
       </c>
       <c r="D622" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E622" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
         <v>7</v>
       </c>
       <c r="D623" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E623" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>7</v>
       </c>
       <c r="D624" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E624" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>7</v>
       </c>
       <c r="D625" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E625" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>7</v>
       </c>
       <c r="D626" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E626" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>7</v>
       </c>
       <c r="D627" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E627" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>7</v>
       </c>
       <c r="D628" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E628" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>7</v>
       </c>
       <c r="D629" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E629" t="inlineStr">
         <is>
@@ -16347,10 +16347,10 @@
         <v>2026</v>
       </c>
       <c r="C630" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D630" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E630" t="inlineStr">
         <is>
@@ -16371,10 +16371,10 @@
         <v>2026</v>
       </c>
       <c r="C631" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D631" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E631" t="inlineStr">
         <is>
@@ -16395,10 +16395,10 @@
         <v>2026</v>
       </c>
       <c r="C632" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D632" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E632" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>8</v>
       </c>
       <c r="D633" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E633" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>8</v>
       </c>
       <c r="D634" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E634" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>8</v>
       </c>
       <c r="D635" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E635" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>8</v>
       </c>
       <c r="D636" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E636" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>8</v>
       </c>
       <c r="D637" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E637" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>8</v>
       </c>
       <c r="D638" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E638" t="inlineStr">
         <is>
@@ -16566,7 +16566,7 @@
         <v>8</v>
       </c>
       <c r="D639" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E639" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>8</v>
       </c>
       <c r="D640" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E640" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>8</v>
       </c>
       <c r="D641" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E641" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>8</v>
       </c>
       <c r="D642" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E642" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>8</v>
       </c>
       <c r="D643" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E643" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>8</v>
       </c>
       <c r="D644" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E644" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>8</v>
       </c>
       <c r="D645" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E645" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>8</v>
       </c>
       <c r="D646" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E646" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>8</v>
       </c>
       <c r="D647" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E647" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>8</v>
       </c>
       <c r="D648" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E648" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>8</v>
       </c>
       <c r="D649" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E649" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>8</v>
       </c>
       <c r="D650" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E650" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>8</v>
       </c>
       <c r="D651" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E651" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>8</v>
       </c>
       <c r="D652" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E652" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>8</v>
       </c>
       <c r="D653" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E653" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>8</v>
       </c>
       <c r="D654" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E654" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>8</v>
       </c>
       <c r="D655" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E655" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>8</v>
       </c>
       <c r="D656" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E656" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>8</v>
       </c>
       <c r="D657" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E657" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>8</v>
       </c>
       <c r="D658" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E658" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>8</v>
       </c>
       <c r="D659" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E659" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>8</v>
       </c>
       <c r="D660" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E660" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>8</v>
       </c>
       <c r="D661" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E661" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>8</v>
       </c>
       <c r="D662" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E662" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>8</v>
       </c>
       <c r="D663" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E663" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>8</v>
       </c>
       <c r="D664" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E664" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>8</v>
       </c>
       <c r="D665" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E665" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>8</v>
       </c>
       <c r="D666" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E666" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>8</v>
       </c>
       <c r="D667" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E667" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>8</v>
       </c>
       <c r="D668" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E668" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>8</v>
       </c>
       <c r="D669" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E669" t="inlineStr">
         <is>
@@ -17307,10 +17307,10 @@
         <v>2026</v>
       </c>
       <c r="C670" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D670" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E670" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         <v>2026</v>
       </c>
       <c r="C671" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D671" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E671" t="inlineStr">
         <is>
@@ -17355,10 +17355,10 @@
         <v>2026</v>
       </c>
       <c r="C672" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D672" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E672" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>9</v>
       </c>
       <c r="D673" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E673" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>9</v>
       </c>
       <c r="D674" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E674" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>9</v>
       </c>
       <c r="D675" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E675" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>9</v>
       </c>
       <c r="D676" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E676" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>9</v>
       </c>
       <c r="D677" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E677" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>9</v>
       </c>
       <c r="D678" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E678" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>9</v>
       </c>
       <c r="D679" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E679" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>9</v>
       </c>
       <c r="D680" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E680" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>9</v>
       </c>
       <c r="D681" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E681" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         <v>9</v>
       </c>
       <c r="D682" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E682" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>9</v>
       </c>
       <c r="D683" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E683" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>9</v>
       </c>
       <c r="D684" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E684" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>9</v>
       </c>
       <c r="D685" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E685" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>9</v>
       </c>
       <c r="D686" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E686" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>9</v>
       </c>
       <c r="D687" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E687" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>9</v>
       </c>
       <c r="D688" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E688" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>9</v>
       </c>
       <c r="D689" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E689" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>9</v>
       </c>
       <c r="D690" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E690" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>9</v>
       </c>
       <c r="D691" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E691" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>9</v>
       </c>
       <c r="D692" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E692" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>9</v>
       </c>
       <c r="D693" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E693" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>9</v>
       </c>
       <c r="D694" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E694" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>9</v>
       </c>
       <c r="D695" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E695" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>9</v>
       </c>
       <c r="D696" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E696" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>9</v>
       </c>
       <c r="D697" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E697" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>9</v>
       </c>
       <c r="D698" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E698" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>9</v>
       </c>
       <c r="D699" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E699" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>9</v>
       </c>
       <c r="D700" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E700" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>9</v>
       </c>
       <c r="D701" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E701" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>9</v>
       </c>
       <c r="D702" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E702" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>9</v>
       </c>
       <c r="D703" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E703" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>9</v>
       </c>
       <c r="D704" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E704" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>9</v>
       </c>
       <c r="D705" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E705" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>9</v>
       </c>
       <c r="D706" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E706" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>9</v>
       </c>
       <c r="D707" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E707" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>9</v>
       </c>
       <c r="D708" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E708" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>9</v>
       </c>
       <c r="D709" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E709" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>9</v>
       </c>
       <c r="D710" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E710" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>9</v>
       </c>
       <c r="D711" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E711" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>9</v>
       </c>
       <c r="D712" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E712" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>9</v>
       </c>
       <c r="D713" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E713" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>9</v>
       </c>
       <c r="D714" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E714" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>9</v>
       </c>
       <c r="D715" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E715" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>9</v>
       </c>
       <c r="D716" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E716" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>9</v>
       </c>
       <c r="D717" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E717" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>9</v>
       </c>
       <c r="D718" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E718" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>9</v>
       </c>
       <c r="D719" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E719" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>9</v>
       </c>
       <c r="D720" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E720" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>9</v>
       </c>
       <c r="D721" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E721" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>9</v>
       </c>
       <c r="D722" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E722" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>9</v>
       </c>
       <c r="D723" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E723" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>9</v>
       </c>
       <c r="D724" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E724" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>9</v>
       </c>
       <c r="D725" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E725" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>9</v>
       </c>
       <c r="D726" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E726" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>9</v>
       </c>
       <c r="D727" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E727" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>9</v>
       </c>
       <c r="D728" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E728" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>9</v>
       </c>
       <c r="D729" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E729" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>9</v>
       </c>
       <c r="D730" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E730" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>9</v>
       </c>
       <c r="D731" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E731" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>9</v>
       </c>
       <c r="D732" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E732" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>9</v>
       </c>
       <c r="D733" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E733" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>9</v>
       </c>
       <c r="D734" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E734" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>9</v>
       </c>
       <c r="D735" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E735" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>9</v>
       </c>
       <c r="D736" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E736" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>9</v>
       </c>
       <c r="D737" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E737" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>9</v>
       </c>
       <c r="D738" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E738" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>9</v>
       </c>
       <c r="D739" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E739" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>9</v>
       </c>
       <c r="D740" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E740" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>9</v>
       </c>
       <c r="D741" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E741" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>9</v>
       </c>
       <c r="D742" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E742" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>9</v>
       </c>
       <c r="D743" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E743" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>9</v>
       </c>
       <c r="D744" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E744" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>9</v>
       </c>
       <c r="D745" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E745" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>9</v>
       </c>
       <c r="D746" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E746" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>9</v>
       </c>
       <c r="D747" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E747" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>9</v>
       </c>
       <c r="D748" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E748" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>9</v>
       </c>
       <c r="D749" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E749" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>9</v>
       </c>
       <c r="D750" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E750" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>9</v>
       </c>
       <c r="D751" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E751" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>9</v>
       </c>
       <c r="D752" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E752" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>9</v>
       </c>
       <c r="D753" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E753" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>9</v>
       </c>
       <c r="D754" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E754" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>9</v>
       </c>
       <c r="D755" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E755" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>9</v>
       </c>
       <c r="D756" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E756" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>9</v>
       </c>
       <c r="D757" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E757" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>9</v>
       </c>
       <c r="D758" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E758" t="inlineStr">
         <is>
@@ -19443,10 +19443,10 @@
         <v>2026</v>
       </c>
       <c r="C759" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D759" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E759" t="inlineStr">
         <is>
@@ -19467,10 +19467,10 @@
         <v>2026</v>
       </c>
       <c r="C760" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D760" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E760" t="inlineStr">
         <is>
@@ -19491,10 +19491,10 @@
         <v>2026</v>
       </c>
       <c r="C761" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D761" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E761" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>10</v>
       </c>
       <c r="D762" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E762" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>10</v>
       </c>
       <c r="D763" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E763" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>10</v>
       </c>
       <c r="D764" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E764" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>10</v>
       </c>
       <c r="D765" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E765" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>10</v>
       </c>
       <c r="D766" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E766" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>10</v>
       </c>
       <c r="D767" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E767" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>10</v>
       </c>
       <c r="D768" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E768" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>10</v>
       </c>
       <c r="D769" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E769" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>10</v>
       </c>
       <c r="D770" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E770" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>10</v>
       </c>
       <c r="D771" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E771" t="inlineStr">
         <is>
@@ -19758,7 +19758,7 @@
         <v>10</v>
       </c>
       <c r="D772" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E772" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>10</v>
       </c>
       <c r="D773" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E773" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>10</v>
       </c>
       <c r="D774" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E774" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>10</v>
       </c>
       <c r="D775" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E775" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>10</v>
       </c>
       <c r="D776" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E776" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>10</v>
       </c>
       <c r="D777" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E777" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>10</v>
       </c>
       <c r="D778" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E778" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>10</v>
       </c>
       <c r="D779" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E779" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>10</v>
       </c>
       <c r="D780" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E780" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>10</v>
       </c>
       <c r="D781" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E781" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>10</v>
       </c>
       <c r="D782" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E782" t="inlineStr">
         <is>
@@ -20022,7 +20022,7 @@
         <v>10</v>
       </c>
       <c r="D783" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E783" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>10</v>
       </c>
       <c r="D784" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E784" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>10</v>
       </c>
       <c r="D785" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E785" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>10</v>
       </c>
       <c r="D786" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E786" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>10</v>
       </c>
       <c r="D787" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E787" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>10</v>
       </c>
       <c r="D788" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E788" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>10</v>
       </c>
       <c r="D789" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E789" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>10</v>
       </c>
       <c r="D790" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E790" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>10</v>
       </c>
       <c r="D791" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E791" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>10</v>
       </c>
       <c r="D792" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E792" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>10</v>
       </c>
       <c r="D793" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E793" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>10</v>
       </c>
       <c r="D794" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E794" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>10</v>
       </c>
       <c r="D795" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E795" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>10</v>
       </c>
       <c r="D796" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E796" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>10</v>
       </c>
       <c r="D797" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E797" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>10</v>
       </c>
       <c r="D798" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E798" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>10</v>
       </c>
       <c r="D799" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E799" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>10</v>
       </c>
       <c r="D800" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E800" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>10</v>
       </c>
       <c r="D801" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E801" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>10</v>
       </c>
       <c r="D802" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E802" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>10</v>
       </c>
       <c r="D803" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E803" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>10</v>
       </c>
       <c r="D804" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E804" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>10</v>
       </c>
       <c r="D805" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E805" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>10</v>
       </c>
       <c r="D806" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E806" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>10</v>
       </c>
       <c r="D807" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E807" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>10</v>
       </c>
       <c r="D808" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E808" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>10</v>
       </c>
       <c r="D809" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E809" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>10</v>
       </c>
       <c r="D810" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E810" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>10</v>
       </c>
       <c r="D811" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E811" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>10</v>
       </c>
       <c r="D812" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E812" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>10</v>
       </c>
       <c r="D813" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E813" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>10</v>
       </c>
       <c r="D814" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E814" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>10</v>
       </c>
       <c r="D815" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E815" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>10</v>
       </c>
       <c r="D816" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E816" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>10</v>
       </c>
       <c r="D817" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E817" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>10</v>
       </c>
       <c r="D818" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E818" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>10</v>
       </c>
       <c r="D819" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E819" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>10</v>
       </c>
       <c r="D820" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E820" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>10</v>
       </c>
       <c r="D821" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E821" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>10</v>
       </c>
       <c r="D822" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E822" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>10</v>
       </c>
       <c r="D823" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E823" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>10</v>
       </c>
       <c r="D824" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E824" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>10</v>
       </c>
       <c r="D825" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E825" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>10</v>
       </c>
       <c r="D826" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E826" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>10</v>
       </c>
       <c r="D827" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E827" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>10</v>
       </c>
       <c r="D828" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E828" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>10</v>
       </c>
       <c r="D829" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E829" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>10</v>
       </c>
       <c r="D830" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E830" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>10</v>
       </c>
       <c r="D831" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E831" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>10</v>
       </c>
       <c r="D832" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E832" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>10</v>
       </c>
       <c r="D833" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E833" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>10</v>
       </c>
       <c r="D834" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E834" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>10</v>
       </c>
       <c r="D835" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E835" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>10</v>
       </c>
       <c r="D836" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E836" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>10</v>
       </c>
       <c r="D837" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E837" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>10</v>
       </c>
       <c r="D838" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E838" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>10</v>
       </c>
       <c r="D839" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E839" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>10</v>
       </c>
       <c r="D840" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E840" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>10</v>
       </c>
       <c r="D841" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E841" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>10</v>
       </c>
       <c r="D842" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E842" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>10</v>
       </c>
       <c r="D843" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E843" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>10</v>
       </c>
       <c r="D844" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E844" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>10</v>
       </c>
       <c r="D845" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E845" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>10</v>
       </c>
       <c r="D846" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E846" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>10</v>
       </c>
       <c r="D847" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E847" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>10</v>
       </c>
       <c r="D848" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E848" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>10</v>
       </c>
       <c r="D849" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E849" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>10</v>
       </c>
       <c r="D850" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E850" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>10</v>
       </c>
       <c r="D851" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E851" t="inlineStr">
         <is>
@@ -21675,10 +21675,10 @@
         <v>2026</v>
       </c>
       <c r="C852" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D852" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E852" t="inlineStr">
         <is>
@@ -21699,10 +21699,10 @@
         <v>2026</v>
       </c>
       <c r="C853" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D853" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E853" t="inlineStr">
         <is>
@@ -21723,10 +21723,10 @@
         <v>2026</v>
       </c>
       <c r="C854" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D854" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E854" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>11</v>
       </c>
       <c r="D855" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E855" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         <v>11</v>
       </c>
       <c r="D856" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E856" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>11</v>
       </c>
       <c r="D857" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E857" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>11</v>
       </c>
       <c r="D858" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E858" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>11</v>
       </c>
       <c r="D859" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E859" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>11</v>
       </c>
       <c r="D860" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E860" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>11</v>
       </c>
       <c r="D861" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E861" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>11</v>
       </c>
       <c r="D862" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E862" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>11</v>
       </c>
       <c r="D863" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E863" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>11</v>
       </c>
       <c r="D864" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E864" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>11</v>
       </c>
       <c r="D865" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E865" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>11</v>
       </c>
       <c r="D866" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E866" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>11</v>
       </c>
       <c r="D867" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E867" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>11</v>
       </c>
       <c r="D868" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E868" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>11</v>
       </c>
       <c r="D869" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E869" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>11</v>
       </c>
       <c r="D870" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E870" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>11</v>
       </c>
       <c r="D871" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E871" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>11</v>
       </c>
       <c r="D872" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E872" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>11</v>
       </c>
       <c r="D873" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E873" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>11</v>
       </c>
       <c r="D874" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E874" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>11</v>
       </c>
       <c r="D875" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E875" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
         <v>11</v>
       </c>
       <c r="D876" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E876" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>11</v>
       </c>
       <c r="D877" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E877" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>11</v>
       </c>
       <c r="D878" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E878" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>11</v>
       </c>
       <c r="D879" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E879" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>11</v>
       </c>
       <c r="D880" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E880" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>11</v>
       </c>
       <c r="D881" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E881" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>11</v>
       </c>
       <c r="D882" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E882" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>11</v>
       </c>
       <c r="D883" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E883" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>11</v>
       </c>
       <c r="D884" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E884" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>11</v>
       </c>
       <c r="D885" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E885" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>11</v>
       </c>
       <c r="D886" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E886" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>11</v>
       </c>
       <c r="D887" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E887" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>11</v>
       </c>
       <c r="D888" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E888" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>11</v>
       </c>
       <c r="D889" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E889" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>11</v>
       </c>
       <c r="D890" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E890" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>11</v>
       </c>
       <c r="D891" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E891" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>11</v>
       </c>
       <c r="D892" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E892" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>11</v>
       </c>
       <c r="D893" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E893" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>11</v>
       </c>
       <c r="D894" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E894" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         <v>11</v>
       </c>
       <c r="D895" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E895" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>11</v>
       </c>
       <c r="D896" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E896" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>11</v>
       </c>
       <c r="D897" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E897" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>11</v>
       </c>
       <c r="D898" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E898" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>11</v>
       </c>
       <c r="D899" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E899" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>11</v>
       </c>
       <c r="D900" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E900" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>11</v>
       </c>
       <c r="D901" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E901" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>11</v>
       </c>
       <c r="D902" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E902" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>11</v>
       </c>
       <c r="D903" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E903" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>11</v>
       </c>
       <c r="D904" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E904" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>11</v>
       </c>
       <c r="D905" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E905" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>11</v>
       </c>
       <c r="D906" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E906" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>11</v>
       </c>
       <c r="D907" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E907" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>11</v>
       </c>
       <c r="D908" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E908" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>11</v>
       </c>
       <c r="D909" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E909" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>11</v>
       </c>
       <c r="D910" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E910" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>11</v>
       </c>
       <c r="D911" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E911" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>11</v>
       </c>
       <c r="D912" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E912" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>11</v>
       </c>
       <c r="D913" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E913" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>11</v>
       </c>
       <c r="D914" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E914" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>11</v>
       </c>
       <c r="D915" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E915" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>11</v>
       </c>
       <c r="D916" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E916" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>11</v>
       </c>
       <c r="D917" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E917" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>11</v>
       </c>
       <c r="D918" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E918" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>11</v>
       </c>
       <c r="D919" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E919" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>11</v>
       </c>
       <c r="D920" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E920" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>11</v>
       </c>
       <c r="D921" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E921" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>11</v>
       </c>
       <c r="D922" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E922" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>11</v>
       </c>
       <c r="D923" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E923" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>11</v>
       </c>
       <c r="D924" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E924" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>11</v>
       </c>
       <c r="D925" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E925" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>11</v>
       </c>
       <c r="D926" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E926" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         <v>11</v>
       </c>
       <c r="D927" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E927" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>11</v>
       </c>
       <c r="D928" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E928" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>11</v>
       </c>
       <c r="D929" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E929" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>11</v>
       </c>
       <c r="D930" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E930" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>11</v>
       </c>
       <c r="D931" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E931" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>11</v>
       </c>
       <c r="D932" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E932" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>11</v>
       </c>
       <c r="D933" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E933" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>11</v>
       </c>
       <c r="D934" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E934" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>11</v>
       </c>
       <c r="D935" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E935" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>11</v>
       </c>
       <c r="D936" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E936" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>11</v>
       </c>
       <c r="D937" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E937" t="inlineStr">
         <is>
@@ -23739,10 +23739,10 @@
         <v>2026</v>
       </c>
       <c r="C938" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D938" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E938" t="inlineStr">
         <is>
@@ -23763,10 +23763,10 @@
         <v>2026</v>
       </c>
       <c r="C939" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D939" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E939" t="inlineStr">
         <is>
@@ -23787,10 +23787,10 @@
         <v>2026</v>
       </c>
       <c r="C940" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D940" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E940" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>12</v>
       </c>
       <c r="D941" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E941" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>12</v>
       </c>
       <c r="D942" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E942" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>12</v>
       </c>
       <c r="D943" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E943" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>12</v>
       </c>
       <c r="D944" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E944" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>12</v>
       </c>
       <c r="D945" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E945" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>12</v>
       </c>
       <c r="D946" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E946" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>12</v>
       </c>
       <c r="D947" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E947" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>12</v>
       </c>
       <c r="D948" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E948" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>12</v>
       </c>
       <c r="D949" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E949" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>12</v>
       </c>
       <c r="D950" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E950" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>12</v>
       </c>
       <c r="D951" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E951" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>12</v>
       </c>
       <c r="D952" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E952" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>12</v>
       </c>
       <c r="D953" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E953" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>12</v>
       </c>
       <c r="D954" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E954" t="inlineStr">
         <is>
@@ -24150,7 +24150,7 @@
         <v>12</v>
       </c>
       <c r="D955" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E955" t="inlineStr">
         <is>
@@ -24174,7 +24174,7 @@
         <v>12</v>
       </c>
       <c r="D956" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E956" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>12</v>
       </c>
       <c r="D957" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E957" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>12</v>
       </c>
       <c r="D958" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E958" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>12</v>
       </c>
       <c r="D959" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E959" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>12</v>
       </c>
       <c r="D960" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E960" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>12</v>
       </c>
       <c r="D961" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E961" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>12</v>
       </c>
       <c r="D962" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E962" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>12</v>
       </c>
       <c r="D963" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E963" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>12</v>
       </c>
       <c r="D964" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E964" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>12</v>
       </c>
       <c r="D965" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E965" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>12</v>
       </c>
       <c r="D966" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E966" t="inlineStr">
         <is>
@@ -24438,7 +24438,7 @@
         <v>12</v>
       </c>
       <c r="D967" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E967" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>12</v>
       </c>
       <c r="D968" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E968" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>12</v>
       </c>
       <c r="D969" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E969" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>12</v>
       </c>
       <c r="D970" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E970" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>12</v>
       </c>
       <c r="D971" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E971" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>12</v>
       </c>
       <c r="D972" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E972" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>12</v>
       </c>
       <c r="D973" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E973" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>12</v>
       </c>
       <c r="D974" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E974" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>12</v>
       </c>
       <c r="D975" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E975" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>12</v>
       </c>
       <c r="D976" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E976" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>12</v>
       </c>
       <c r="D977" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E977" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>12</v>
       </c>
       <c r="D978" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E978" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>12</v>
       </c>
       <c r="D979" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E979" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>12</v>
       </c>
       <c r="D980" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E980" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>12</v>
       </c>
       <c r="D981" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E981" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>12</v>
       </c>
       <c r="D982" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E982" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>12</v>
       </c>
       <c r="D983" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E983" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>12</v>
       </c>
       <c r="D984" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E984" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>12</v>
       </c>
       <c r="D985" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E985" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>12</v>
       </c>
       <c r="D986" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E986" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>12</v>
       </c>
       <c r="D987" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E987" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>12</v>
       </c>
       <c r="D988" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E988" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>12</v>
       </c>
       <c r="D989" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E989" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>12</v>
       </c>
       <c r="D990" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E990" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>12</v>
       </c>
       <c r="D991" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E991" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>12</v>
       </c>
       <c r="D992" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E992" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>12</v>
       </c>
       <c r="D993" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E993" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>12</v>
       </c>
       <c r="D994" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E994" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>12</v>
       </c>
       <c r="D995" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E995" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>12</v>
       </c>
       <c r="D996" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E996" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>12</v>
       </c>
       <c r="D997" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E997" t="inlineStr">
         <is>
@@ -25182,7 +25182,7 @@
         <v>12</v>
       </c>
       <c r="D998" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E998" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>12</v>
       </c>
       <c r="D999" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E999" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>12</v>
       </c>
       <c r="D1000" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E1000" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>12</v>
       </c>
       <c r="D1001" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E1001" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>12</v>
       </c>
       <c r="D1002" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E1002" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>12</v>
       </c>
       <c r="D1003" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1003" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>12</v>
       </c>
       <c r="D1004" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1004" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>12</v>
       </c>
       <c r="D1005" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1005" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>12</v>
       </c>
       <c r="D1006" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E1006" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>12</v>
       </c>
       <c r="D1007" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E1007" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>12</v>
       </c>
       <c r="D1008" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E1008" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>12</v>
       </c>
       <c r="D1009" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E1009" t="inlineStr">
         <is>
@@ -25470,7 +25470,7 @@
         <v>12</v>
       </c>
       <c r="D1010" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E1010" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>12</v>
       </c>
       <c r="D1011" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E1011" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>12</v>
       </c>
       <c r="D1012" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E1012" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>12</v>
       </c>
       <c r="D1013" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E1013" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>12</v>
       </c>
       <c r="D1014" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E1014" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>12</v>
       </c>
       <c r="D1015" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E1015" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>12</v>
       </c>
       <c r="D1016" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E1016" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>12</v>
       </c>
       <c r="D1017" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E1017" t="inlineStr">
         <is>
@@ -25841,7 +25841,6 @@
           <t>Otro</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>#FCD34D</t>
